--- a/server/data/cheque/modifiedCheque.xlsx
+++ b/server/data/cheque/modifiedCheque.xlsx
@@ -397,10 +397,105 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetData/>
+  <dimension ref="A1:O2"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Cheque no</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Bank Account</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Payee</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Payment Date</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Memo</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Global Tax Calculation</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Expense Account</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Expense Description</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Expense Line Amount</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Expense Tax Code</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Expense Account Tax Amount</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Expense Class</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Currency Code</v>
+      </c>
+      <c r="N1" t="str">
+        <v>Exchange Rate</v>
+      </c>
+      <c r="O1" t="str">
+        <v>Expense Customer</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1843_</v>
+      </c>
+      <c r="B2" t="str">
+        <v>FNB Cheque</v>
+      </c>
+      <c r="C2" t="str">
+        <v>ACTSYS Cable &amp; Wireless Solutions</v>
+      </c>
+      <c r="D2" t="str">
+        <v>03/06/2022</v>
+      </c>
+      <c r="E2" t="str">
+        <v>FNB OB 000000917 ACTSYS</v>
+      </c>
+      <c r="F2" t="str">
+        <v>TaxExcluded</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Accounts Payable (A/P)</v>
+      </c>
+      <c r="H2" t="str">
+        <v>FNB OB 000000917 ACTSYS</v>
+      </c>
+      <c r="I2">
+        <v>8705.8</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Out of Scope</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
+        <v>ZAR</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O2"/>
   </ignoredErrors>
 </worksheet>
 </file>